--- a/data/data_raw/eurostat/AT_rail_tracks_rail_if_line_tr.xlsx
+++ b/data/data_raw/eurostat/AT_rail_tracks_rail_if_line_tr.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -755,6 +760,9 @@
       </c>
       <c r="AN2" t="n">
         <v>3291</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3328</v>
       </c>
     </row>
     <row r="3">
@@ -888,6 +896,9 @@
       <c r="AN3" t="n">
         <v>2286</v>
       </c>
+      <c r="AO3" t="n">
+        <v>2296</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1020,6 +1031,9 @@
       <c r="AN4" t="n">
         <v>5577</v>
       </c>
+      <c r="AO4" t="n">
+        <v>5624</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1152,6 +1166,9 @@
       <c r="AN5" t="n">
         <v>1869</v>
       </c>
+      <c r="AO5" t="n">
+        <v>1898</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1284,6 +1301,9 @@
       <c r="AN6" t="n">
         <v>2251</v>
       </c>
+      <c r="AO6" t="n">
+        <v>2264</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1416,6 +1436,9 @@
       <c r="AN7" t="n">
         <v>4119</v>
       </c>
+      <c r="AO7" t="n">
+        <v>4161</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1548,6 +1571,9 @@
       <c r="AN8" t="n">
         <v>1422</v>
       </c>
+      <c r="AO8" t="n">
+        <v>1430</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1680,6 +1706,9 @@
       <c r="AN9" t="n">
         <v>35</v>
       </c>
+      <c r="AO9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1811,6 +1840,9 @@
       </c>
       <c r="AN10" t="n">
         <v>1458</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1463</v>
       </c>
     </row>
   </sheetData>
